--- a/lab-2/regvals.xlsx
+++ b/lab-2/regvals.xlsx
@@ -428,6 +428,9 @@
   </sheetPr>
   <dimension ref="A1:AK46"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="2" style="0" width="2.5"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
@@ -4869,7 +4872,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S46" s="6" t="s">
+      <c r="Q46" s="6" t="s">
         <v>2</v>
       </c>
     </row>
